--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{2F8C1C08-9A4D-6044-B8B2-D471674F7BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E31587EB-AFEF-4946-92F4-10B75822ACA8}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{2F8C1C08-9A4D-6044-B8B2-D471674F7BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AC8A5C-2403-E04D-8AFC-2302CB3A59DE}"/>
   <bookViews>
     <workbookView xWindow="-28500" yWindow="760" windowWidth="27820" windowHeight="21420" xr2:uid="{94B0D7C2-568F-A244-B31E-6B29F3B33498}"/>
   </bookViews>
@@ -460,9 +460,6 @@
     <t>Vasc.Endo.2</t>
   </si>
   <si>
-    <t>Macro</t>
-  </si>
-  <si>
     <t>Neuron_ambig</t>
   </si>
   <si>
@@ -473,6 +470,9 @@
   </si>
   <si>
     <t>Vasc.VLMC.4</t>
+  </si>
+  <si>
+    <t>Macrophage</t>
   </si>
 </sst>
 </file>
@@ -1382,7 +1382,7 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O1" t="s">
         <v>13</v>
@@ -1709,7 +1709,7 @@
         <v>94</v>
       </c>
       <c r="Q7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -2027,7 +2027,7 @@
         <v>113</v>
       </c>
       <c r="Q13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -2080,7 +2080,7 @@
         <v>123</v>
       </c>
       <c r="Q14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
@@ -2610,7 +2610,7 @@
         <v>118</v>
       </c>
       <c r="Q24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
@@ -3034,7 +3034,7 @@
         <v>56</v>
       </c>
       <c r="Q32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">

--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{2F8C1C08-9A4D-6044-B8B2-D471674F7BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AC8A5C-2403-E04D-8AFC-2302CB3A59DE}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{2F8C1C08-9A4D-6044-B8B2-D471674F7BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67E9710D-43EE-7E4A-A568-A169616B30DA}"/>
   <bookViews>
     <workbookView xWindow="-28500" yWindow="760" windowWidth="27820" windowHeight="21420" xr2:uid="{94B0D7C2-568F-A244-B31E-6B29F3B33498}"/>
   </bookViews>

--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/var/folders/8j/ftgpc01j3vx744_jxfrp_1rc0000gn/T/ch.sudo.cyberduck/editor-2e410720-64de-4a9d-afe0-3aade0a842b4/39743821f4f6107b013628435f237b33/614260095/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{2F8C1C08-9A4D-6044-B8B2-D471674F7BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87AC8A5C-2403-E04D-8AFC-2302CB3A59DE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B51FB27-7B9F-424B-B085-152D0E3436FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28500" yWindow="760" windowWidth="27820" windowHeight="21420" xr2:uid="{94B0D7C2-568F-A244-B31E-6B29F3B33498}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="153">
   <si>
     <t>k10</t>
   </si>
@@ -460,9 +460,6 @@
     <t>Vasc.Endo.2</t>
   </si>
   <si>
-    <t>Neuron_ambig</t>
-  </si>
-  <si>
     <t>OPC.5</t>
   </si>
   <si>
@@ -472,14 +469,26 @@
     <t>Vasc.VLMC.4</t>
   </si>
   <si>
-    <t>Macrophage</t>
+    <t>Oligo.Neu.1</t>
+  </si>
+  <si>
+    <t>Oligo.Neu.2</t>
+  </si>
+  <si>
+    <t>Macro</t>
+  </si>
+  <si>
+    <t>cell_type_broad</t>
+  </si>
+  <si>
+    <t>Vasc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -610,6 +619,12 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1334,14 +1349,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA5E195-4214-724F-A2F9-342B301003E9}">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1397,7 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O1" t="s">
         <v>13</v>
@@ -1393,8 +1408,11 @@
       <c r="Q1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1446,8 +1464,11 @@
       <c r="Q2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1499,8 +1520,11 @@
       <c r="Q3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1552,8 +1576,11 @@
       <c r="Q4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1605,8 +1632,11 @@
       <c r="Q5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1658,8 +1688,11 @@
       <c r="Q6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1709,10 +1742,13 @@
         <v>94</v>
       </c>
       <c r="Q7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+      <c r="R7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1764,8 +1800,11 @@
       <c r="Q8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1817,8 +1856,11 @@
       <c r="Q9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1870,8 +1912,11 @@
       <c r="Q10" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1923,8 +1968,11 @@
       <c r="Q11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1976,8 +2024,11 @@
       <c r="Q12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2027,10 +2078,13 @@
         <v>113</v>
       </c>
       <c r="Q13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+        <v>148</v>
+      </c>
+      <c r="R13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -2080,10 +2134,13 @@
         <v>123</v>
       </c>
       <c r="Q14" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="R14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2135,8 +2192,11 @@
       <c r="Q15" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2188,8 +2248,11 @@
       <c r="Q16" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2241,8 +2304,11 @@
       <c r="Q17" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -2294,8 +2360,11 @@
       <c r="Q18" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2347,8 +2416,11 @@
       <c r="Q19" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -2400,8 +2472,11 @@
       <c r="Q20" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -2453,8 +2528,11 @@
       <c r="Q21" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -2506,8 +2584,11 @@
       <c r="Q22" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -2559,8 +2640,11 @@
       <c r="Q23" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -2610,10 +2694,13 @@
         <v>118</v>
       </c>
       <c r="Q24" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+      <c r="R24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -2665,8 +2752,11 @@
       <c r="Q25" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -2718,8 +2808,11 @@
       <c r="Q26" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2771,8 +2864,11 @@
       <c r="Q27" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2824,8 +2920,11 @@
       <c r="Q28" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -2877,8 +2976,11 @@
       <c r="Q29" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -2930,8 +3032,11 @@
       <c r="Q30" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -2983,8 +3088,11 @@
       <c r="Q31" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -3034,10 +3142,13 @@
         <v>56</v>
       </c>
       <c r="Q32" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="R32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -3087,10 +3198,13 @@
         <v>16</v>
       </c>
       <c r="Q33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="R33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -3140,10 +3254,13 @@
         <v>16</v>
       </c>
       <c r="Q34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="R34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -3193,10 +3310,13 @@
         <v>16</v>
       </c>
       <c r="Q35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="R35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>42</v>
       </c>
@@ -3246,10 +3366,13 @@
         <v>16</v>
       </c>
       <c r="Q36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="R36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -3299,10 +3422,13 @@
         <v>16</v>
       </c>
       <c r="Q37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="R37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -3352,10 +3478,13 @@
         <v>16</v>
       </c>
       <c r="Q38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="R38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -3405,10 +3534,13 @@
         <v>16</v>
       </c>
       <c r="Q39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="R39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -3458,10 +3590,13 @@
         <v>16</v>
       </c>
       <c r="Q40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="R40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3511,10 +3646,13 @@
         <v>16</v>
       </c>
       <c r="Q41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="R41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -3564,7 +3702,10 @@
         <v>16</v>
       </c>
       <c r="Q42" t="s">
-        <v>16</v>
+        <v>126</v>
+      </c>
+      <c r="R42" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3573,6 +3714,7 @@
       <sortCondition descending="1" ref="C1:C42"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2708ABB4-B831-8549-AEE2-56245E99D395}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAAB6027-9473-7F4B-994C-AA4EA26C9B77}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="920" windowWidth="28040" windowHeight="17440" xr2:uid="{D28FA05A-120C-6545-B4F5-F747CF17E917}"/>
   </bookViews>
@@ -475,9 +475,6 @@
     <t>cell_type_anno</t>
   </si>
   <si>
-    <t>Vasc.VLCM</t>
-  </si>
-  <si>
     <t>Vasc.PC</t>
   </si>
   <si>
@@ -491,6 +488,9 @@
   </si>
   <si>
     <t>OPC.5</t>
+  </si>
+  <si>
+    <t>Vasc.VLMC</t>
   </si>
 </sst>
 </file>
@@ -2119,7 +2119,7 @@
         <v>81</v>
       </c>
       <c r="S13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
@@ -3004,7 +3004,7 @@
         <v>125</v>
       </c>
       <c r="S28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -3063,7 +3063,7 @@
         <v>125</v>
       </c>
       <c r="S29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -3358,7 +3358,7 @@
         <v>130</v>
       </c>
       <c r="S34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
@@ -3417,7 +3417,7 @@
         <v>64</v>
       </c>
       <c r="S35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -3476,7 +3476,7 @@
         <v>19</v>
       </c>
       <c r="S36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -3535,7 +3535,7 @@
         <v>64</v>
       </c>
       <c r="S37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
@@ -3594,7 +3594,7 @@
         <v>64</v>
       </c>
       <c r="S38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -3653,7 +3653,7 @@
         <v>64</v>
       </c>
       <c r="S39" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
@@ -3712,7 +3712,7 @@
         <v>64</v>
       </c>
       <c r="S40" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -3771,7 +3771,7 @@
         <v>64</v>
       </c>
       <c r="S41" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
@@ -3830,7 +3830,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAAB6027-9473-7F4B-994C-AA4EA26C9B77}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A19C9821-8A27-664E-9195-3CA780F7D060}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="920" windowWidth="28040" windowHeight="17440" xr2:uid="{D28FA05A-120C-6545-B4F5-F747CF17E917}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="ERCsn_glia_subcluster_info" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ERCsn_glia_subcluster_info!$A$1:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ERCsn_glia_subcluster_info!$A$1:$T$42</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="157">
   <si>
     <t>k10</t>
   </si>
@@ -64,9 +64,6 @@
     <t>snDLPFC_PEC</t>
   </si>
   <si>
-    <t>cell_type_broad</t>
-  </si>
-  <si>
     <t>DGE_compat</t>
   </si>
   <si>
@@ -491,6 +488,12 @@
   </si>
   <si>
     <t>Vasc.VLMC</t>
+  </si>
+  <si>
+    <t>cell_type_broad_og</t>
+  </si>
+  <si>
+    <t>Vasc</t>
   </si>
 </sst>
 </file>
@@ -1352,10 +1355,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921EB8AC-600C-6545-A6FA-27BF07546C43}">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1396,27 +1399,30 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
+        <v>155</v>
+      </c>
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>18</v>
       </c>
       <c r="B2">
         <v>10976</v>
@@ -1425,13 +1431,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
       </c>
       <c r="G2">
         <v>9395</v>
@@ -1446,36 +1452,39 @@
         <v>1.0052856523543501E-3</v>
       </c>
       <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>23</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
         <v>24</v>
       </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>27</v>
       </c>
       <c r="B3">
         <v>5276</v>
@@ -1484,13 +1493,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
         <v>3337</v>
@@ -1505,36 +1514,39 @@
         <v>7.34380388166755E-4</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>31</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>32</v>
       </c>
       <c r="B4">
         <v>3087</v>
@@ -1543,13 +1555,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>5406</v>
@@ -1564,36 +1576,39 @@
         <v>9.2488911468535597E-4</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
         <v>34</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>35</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>36</v>
       </c>
       <c r="B5">
         <v>1133</v>
@@ -1602,13 +1617,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <v>7658</v>
@@ -1623,34 +1638,37 @@
         <v>1.22074235696345E-3</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" t="s">
         <v>38</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
         <v>39</v>
       </c>
-      <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="s">
-        <v>40</v>
-      </c>
       <c r="Q5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1661,13 +1679,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6">
         <v>1847.5</v>
@@ -1682,36 +1700,39 @@
         <v>7.4577931081876105E-4</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>24</v>
-      </c>
-      <c r="R6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>43</v>
       </c>
       <c r="B7">
         <v>384</v>
@@ -1720,13 +1741,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7">
         <v>1165</v>
@@ -1741,36 +1762,39 @@
         <v>6.3512404449284001E-4</v>
       </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>46</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -1779,13 +1803,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8">
         <v>14575</v>
@@ -1800,36 +1824,39 @@
         <v>0.99919372797012296</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>49</v>
       </c>
       <c r="B9">
         <v>81</v>
@@ -1838,13 +1865,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>26876</v>
@@ -1859,36 +1886,39 @@
         <v>0.99924951791763295</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="T9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10">
         <v>47</v>
@@ -1897,13 +1927,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>585</v>
@@ -1918,36 +1948,39 @@
         <v>6.7282974487170501E-4</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S10" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>54</v>
       </c>
       <c r="B11">
         <v>47</v>
@@ -1956,13 +1989,13 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>53380</v>
@@ -1977,36 +2010,39 @@
         <v>0.99924832582473699</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S11" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>56</v>
       </c>
       <c r="B12">
         <v>22</v>
@@ -2015,13 +2051,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>859</v>
@@ -2036,36 +2072,39 @@
         <v>8.3860030281357402E-4</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="T12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>433</v>
@@ -2074,13 +2113,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G13">
         <v>4066</v>
@@ -2095,36 +2134,39 @@
         <v>8.0070935655385202E-4</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L13" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" t="s">
         <v>99</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
         <v>100</v>
       </c>
-      <c r="N13" t="s">
-        <v>86</v>
-      </c>
-      <c r="O13" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>101</v>
       </c>
-      <c r="Q13" t="s">
-        <v>102</v>
-      </c>
       <c r="R13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="T13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>4227</v>
@@ -2133,13 +2175,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G14">
         <v>4598</v>
@@ -2154,36 +2196,39 @@
         <v>7.7069737017154596E-4</v>
       </c>
       <c r="K14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s">
         <v>84</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>85</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
         <v>86</v>
       </c>
-      <c r="N14" t="s">
-        <v>86</v>
-      </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" t="s">
         <v>87</v>
       </c>
-      <c r="Q14" t="s">
-        <v>86</v>
-      </c>
-      <c r="R14" t="s">
-        <v>88</v>
-      </c>
       <c r="S14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="T14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>3748</v>
@@ -2192,13 +2237,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15">
         <v>2557.5</v>
@@ -2213,36 +2258,39 @@
         <v>7.5151113560423201E-4</v>
       </c>
       <c r="K15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" t="s">
         <v>90</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" t="s">
         <v>91</v>
       </c>
-      <c r="N15" t="s">
-        <v>86</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>86</v>
-      </c>
-      <c r="R15" t="s">
-        <v>92</v>
-      </c>
       <c r="S15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="T15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16">
         <v>1876</v>
@@ -2251,13 +2299,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16">
         <v>4734.5</v>
@@ -2272,36 +2320,39 @@
         <v>7.9788090079091403E-4</v>
       </c>
       <c r="K16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" t="s">
         <v>84</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
+        <v>93</v>
+      </c>
+      <c r="N16" t="s">
         <v>85</v>
       </c>
-      <c r="M16" t="s">
-        <v>94</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
         <v>86</v>
       </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" t="s">
-        <v>87</v>
-      </c>
       <c r="Q16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="T16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>1728</v>
@@ -2310,13 +2361,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17">
         <v>4342.5</v>
@@ -2331,36 +2382,39 @@
         <v>7.7069737017154596E-4</v>
       </c>
       <c r="K17" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s">
         <v>84</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
+        <v>93</v>
+      </c>
+      <c r="N17" t="s">
         <v>85</v>
       </c>
-      <c r="M17" t="s">
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" t="s">
+        <v>85</v>
+      </c>
+      <c r="T17" t="s">
         <v>94</v>
       </c>
-      <c r="N17" t="s">
-        <v>86</v>
-      </c>
-      <c r="O17" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>86</v>
-      </c>
-      <c r="R17" t="s">
-        <v>88</v>
-      </c>
-      <c r="S17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>590</v>
@@ -2369,13 +2423,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G18">
         <v>2510</v>
@@ -2390,36 +2444,39 @@
         <v>7.9654873115941795E-4</v>
       </c>
       <c r="K18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N18" t="s">
+        <v>85</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
         <v>86</v>
       </c>
-      <c r="O18" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" t="s">
-        <v>87</v>
-      </c>
       <c r="Q18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="T18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>802</v>
@@ -2428,13 +2485,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19">
         <v>1497.5</v>
@@ -2449,36 +2506,39 @@
         <v>7.1135553298517997E-4</v>
       </c>
       <c r="K19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="T19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <v>124</v>
@@ -2487,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20">
         <v>7586.5</v>
@@ -2508,36 +2568,39 @@
         <v>0.99873107671737604</v>
       </c>
       <c r="K20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S20" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="T20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>12519</v>
@@ -2546,13 +2609,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G21">
         <v>5673</v>
@@ -2567,36 +2630,39 @@
         <v>1.1913639027625301E-3</v>
       </c>
       <c r="K21" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21" t="s">
         <v>107</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>108</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
+        <v>108</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>108</v>
+      </c>
+      <c r="R21" t="s">
         <v>109</v>
       </c>
-      <c r="N21" t="s">
-        <v>109</v>
-      </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="S21" t="s">
         <v>108</v>
       </c>
-      <c r="Q21" t="s">
-        <v>109</v>
-      </c>
-      <c r="R21" t="s">
-        <v>110</v>
-      </c>
-      <c r="S21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>12010</v>
@@ -2605,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G22">
         <v>8807</v>
@@ -2626,36 +2692,39 @@
         <v>1.84304174035787E-3</v>
       </c>
       <c r="K22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" t="s">
+        <v>108</v>
+      </c>
+      <c r="N22" t="s">
+        <v>108</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
         <v>112</v>
       </c>
-      <c r="M22" t="s">
+      <c r="Q22" t="s">
+        <v>108</v>
+      </c>
+      <c r="R22" t="s">
         <v>109</v>
       </c>
-      <c r="N22" t="s">
-        <v>109</v>
-      </c>
-      <c r="O22" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>109</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
+        <v>108</v>
+      </c>
+      <c r="T22" t="s">
         <v>110</v>
       </c>
-      <c r="S22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23">
         <v>8587</v>
@@ -2664,13 +2733,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G23">
         <v>2161</v>
@@ -2685,36 +2754,39 @@
         <v>7.5151113560423201E-4</v>
       </c>
       <c r="K23" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" t="s">
+        <v>114</v>
+      </c>
+      <c r="M23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N23" t="s">
+        <v>108</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="s">
         <v>107</v>
       </c>
-      <c r="L23" t="s">
+      <c r="Q23" t="s">
+        <v>108</v>
+      </c>
+      <c r="R23" t="s">
         <v>115</v>
       </c>
-      <c r="M23" t="s">
-        <v>63</v>
-      </c>
-      <c r="N23" t="s">
-        <v>109</v>
-      </c>
-      <c r="O23" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="S23" t="s">
         <v>108</v>
       </c>
-      <c r="Q23" t="s">
-        <v>109</v>
-      </c>
-      <c r="R23" t="s">
-        <v>116</v>
-      </c>
-      <c r="S23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24">
         <v>6911</v>
@@ -2723,13 +2795,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24">
         <v>3616</v>
@@ -2744,36 +2816,39 @@
         <v>9.9148368462920211E-4</v>
       </c>
       <c r="K24" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" t="s">
         <v>107</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>108</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
+        <v>108</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>108</v>
+      </c>
+      <c r="R24" t="s">
         <v>109</v>
       </c>
-      <c r="N24" t="s">
-        <v>109</v>
-      </c>
-      <c r="O24" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>109</v>
-      </c>
-      <c r="R24" t="s">
-        <v>110</v>
-      </c>
       <c r="S24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25">
         <v>4254</v>
@@ -2782,13 +2857,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G25">
         <v>3743.5</v>
@@ -2803,36 +2878,39 @@
         <v>9.7419167286716402E-4</v>
       </c>
       <c r="K25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L25" t="s">
+        <v>118</v>
+      </c>
+      <c r="M25" t="s">
         <v>119</v>
       </c>
-      <c r="M25" t="s">
-        <v>120</v>
-      </c>
       <c r="N25" t="s">
+        <v>108</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>108</v>
+      </c>
+      <c r="R25" t="s">
         <v>109</v>
       </c>
-      <c r="O25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P25" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>109</v>
-      </c>
-      <c r="R25" t="s">
-        <v>110</v>
-      </c>
       <c r="S25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>812</v>
@@ -2841,13 +2919,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G26">
         <v>1111</v>
@@ -2862,36 +2940,39 @@
         <v>7.02247663866728E-4</v>
       </c>
       <c r="K26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S26" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27">
         <v>118</v>
@@ -2900,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27">
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G27">
         <v>8577</v>
@@ -2921,36 +3002,39 @@
         <v>0.99896824359893799</v>
       </c>
       <c r="K27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S27" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B28">
         <v>535</v>
@@ -2959,13 +3043,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G28">
         <v>3158</v>
@@ -2980,36 +3064,39 @@
         <v>1.23374222312122E-3</v>
       </c>
       <c r="K28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L28" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28" t="s">
         <v>122</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
+        <v>108</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="s">
         <v>123</v>
       </c>
-      <c r="N28" t="s">
-        <v>109</v>
-      </c>
-      <c r="O28" t="b">
-        <v>1</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
+        <v>122</v>
+      </c>
+      <c r="R28" t="s">
         <v>124</v>
       </c>
-      <c r="Q28" t="s">
-        <v>123</v>
-      </c>
-      <c r="R28" t="s">
-        <v>125</v>
-      </c>
       <c r="S28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B29">
         <v>427</v>
@@ -3018,13 +3105,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G29">
         <v>6994</v>
@@ -3039,36 +3126,39 @@
         <v>1.19990780949592E-2</v>
       </c>
       <c r="K29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L29" t="s">
+        <v>131</v>
+      </c>
+      <c r="M29" t="s">
         <v>132</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
+        <v>108</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" t="s">
         <v>133</v>
       </c>
-      <c r="N29" t="s">
-        <v>109</v>
-      </c>
-      <c r="O29" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>134</v>
       </c>
-      <c r="Q29" t="s">
-        <v>135</v>
-      </c>
       <c r="R29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S29" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>4815</v>
@@ -3077,13 +3167,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G30">
         <v>8122</v>
@@ -3098,36 +3188,39 @@
         <v>1.0560568189248399E-3</v>
       </c>
       <c r="K30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L30" t="s">
+        <v>139</v>
+      </c>
+      <c r="M30" t="s">
+        <v>140</v>
+      </c>
+      <c r="N30" t="s">
+        <v>128</v>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
         <v>127</v>
       </c>
-      <c r="L30" t="s">
-        <v>140</v>
-      </c>
-      <c r="M30" t="s">
-        <v>141</v>
-      </c>
-      <c r="N30" t="s">
+      <c r="Q30" t="s">
+        <v>128</v>
+      </c>
+      <c r="R30" t="s">
         <v>129</v>
       </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" t="s">
+      <c r="S30" t="s">
         <v>128</v>
       </c>
-      <c r="Q30" t="s">
-        <v>129</v>
-      </c>
-      <c r="R30" t="s">
-        <v>130</v>
-      </c>
-      <c r="S30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31">
         <v>4009</v>
@@ -3136,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G31">
         <v>4601</v>
@@ -3157,36 +3250,39 @@
         <v>8.0116966273635604E-4</v>
       </c>
       <c r="K31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L31" t="s">
+        <v>142</v>
+      </c>
+      <c r="M31" t="s">
+        <v>143</v>
+      </c>
+      <c r="N31" t="s">
+        <v>128</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="s">
         <v>127</v>
       </c>
-      <c r="L31" t="s">
-        <v>143</v>
-      </c>
-      <c r="M31" t="s">
-        <v>144</v>
-      </c>
-      <c r="N31" t="s">
+      <c r="Q31" t="s">
+        <v>128</v>
+      </c>
+      <c r="R31" t="s">
         <v>129</v>
       </c>
-      <c r="O31" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="S31" t="s">
         <v>128</v>
       </c>
-      <c r="Q31" t="s">
-        <v>129</v>
-      </c>
-      <c r="R31" t="s">
-        <v>130</v>
-      </c>
-      <c r="S31" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32">
         <v>3932</v>
@@ -3195,13 +3291,13 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G32">
         <v>12043.5</v>
@@ -3216,36 +3312,39 @@
         <v>1.50453706737607E-3</v>
       </c>
       <c r="K32" t="s">
+        <v>126</v>
+      </c>
+      <c r="L32" t="s">
+        <v>145</v>
+      </c>
+      <c r="M32" t="s">
+        <v>34</v>
+      </c>
+      <c r="N32" t="s">
+        <v>128</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="s">
         <v>127</v>
       </c>
-      <c r="L32" t="s">
-        <v>146</v>
-      </c>
-      <c r="M32" t="s">
-        <v>35</v>
-      </c>
-      <c r="N32" t="s">
+      <c r="Q32" t="s">
+        <v>128</v>
+      </c>
+      <c r="R32" t="s">
         <v>129</v>
       </c>
-      <c r="O32" t="b">
-        <v>1</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="S32" t="s">
         <v>128</v>
       </c>
-      <c r="Q32" t="s">
-        <v>129</v>
-      </c>
-      <c r="R32" t="s">
-        <v>130</v>
-      </c>
-      <c r="S32" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33">
         <v>1961</v>
@@ -3254,13 +3353,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G33">
         <v>10767</v>
@@ -3275,36 +3374,39 @@
         <v>1.2470565270632501E-3</v>
       </c>
       <c r="K33" t="s">
+        <v>126</v>
+      </c>
+      <c r="L33" t="s">
+        <v>147</v>
+      </c>
+      <c r="M33" t="s">
+        <v>34</v>
+      </c>
+      <c r="N33" t="s">
+        <v>128</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
         <v>127</v>
       </c>
-      <c r="L33" t="s">
-        <v>148</v>
-      </c>
-      <c r="M33" t="s">
-        <v>35</v>
-      </c>
-      <c r="N33" t="s">
+      <c r="Q33" t="s">
+        <v>128</v>
+      </c>
+      <c r="R33" t="s">
         <v>129</v>
       </c>
-      <c r="O33" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="S33" t="s">
         <v>128</v>
       </c>
-      <c r="Q33" t="s">
-        <v>129</v>
-      </c>
-      <c r="R33" t="s">
-        <v>130</v>
-      </c>
-      <c r="S33" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34">
         <v>458</v>
@@ -3313,13 +3415,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34">
         <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G34">
         <v>2204</v>
@@ -3334,36 +3436,39 @@
         <v>6.5941060893237504E-4</v>
       </c>
       <c r="K34" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" t="s">
         <v>127</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
         <v>128</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
+        <v>108</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>128</v>
+      </c>
+      <c r="R34" t="s">
         <v>129</v>
       </c>
-      <c r="N34" t="s">
-        <v>109</v>
-      </c>
-      <c r="O34" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" t="s">
+      <c r="S34" t="s">
         <v>128</v>
       </c>
-      <c r="Q34" t="s">
-        <v>129</v>
-      </c>
-      <c r="R34" t="s">
-        <v>130</v>
-      </c>
-      <c r="S34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35">
         <v>345</v>
@@ -3372,13 +3477,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G35">
         <v>7872</v>
@@ -3393,36 +3498,39 @@
         <v>1.4534917427226901E-3</v>
       </c>
       <c r="K35" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" t="s">
         <v>66</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
+        <v>60</v>
+      </c>
+      <c r="N35" t="s">
+        <v>60</v>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" t="s">
         <v>67</v>
       </c>
-      <c r="M35" t="s">
-        <v>61</v>
-      </c>
-      <c r="N35" t="s">
-        <v>61</v>
-      </c>
-      <c r="O35" t="b">
-        <v>1</v>
-      </c>
-      <c r="P35" t="s">
-        <v>68</v>
-      </c>
       <c r="Q35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S35" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T35" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36">
         <v>41</v>
@@ -3431,13 +3539,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36">
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G36">
         <v>7117</v>
@@ -3452,34 +3560,37 @@
         <v>1.4361247885972201E-3</v>
       </c>
       <c r="K36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
       <c r="P36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S36" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -3490,13 +3601,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E37">
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G37">
         <v>4861.5</v>
@@ -3511,36 +3622,39 @@
         <v>1.1913639027625301E-3</v>
       </c>
       <c r="K37" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" t="s">
         <v>66</v>
       </c>
-      <c r="L37" t="s">
-        <v>67</v>
-      </c>
       <c r="M37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S37" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T37" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38">
         <v>147</v>
@@ -3549,13 +3663,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G38">
         <v>6357</v>
@@ -3570,36 +3684,39 @@
         <v>1.4223176985979E-3</v>
       </c>
       <c r="K38" t="s">
+        <v>73</v>
+      </c>
+      <c r="L38" t="s">
         <v>74</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>75</v>
       </c>
-      <c r="M38" t="s">
-        <v>76</v>
-      </c>
       <c r="N38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
       </c>
       <c r="P38" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q38" t="s">
         <v>75</v>
       </c>
-      <c r="Q38" t="s">
-        <v>76</v>
-      </c>
       <c r="R38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S38" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T38" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39">
         <v>352</v>
@@ -3608,13 +3725,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G39">
         <v>5216.5</v>
@@ -3629,36 +3746,39 @@
         <v>1.0071775759570301E-3</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" t="s">
         <v>59</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>60</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" t="s">
         <v>61</v>
       </c>
-      <c r="O39" t="b">
-        <v>1</v>
-      </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>62</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>63</v>
       </c>
-      <c r="R39" t="s">
-        <v>64</v>
-      </c>
       <c r="S39" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T39" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40">
         <v>286</v>
@@ -3667,13 +3787,13 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40">
         <v>8664</v>
@@ -3688,36 +3808,39 @@
         <v>1.2288140133023199E-3</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M40" t="s">
+        <v>62</v>
+      </c>
+      <c r="N40" t="s">
+        <v>60</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>62</v>
+      </c>
+      <c r="R40" t="s">
         <v>63</v>
       </c>
-      <c r="N40" t="s">
-        <v>61</v>
-      </c>
-      <c r="O40" t="b">
-        <v>1</v>
-      </c>
-      <c r="P40" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>63</v>
-      </c>
-      <c r="R40" t="s">
-        <v>64</v>
-      </c>
       <c r="S40" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T40" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41">
         <v>212</v>
@@ -3726,13 +3849,13 @@
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41">
         <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G41">
         <v>6566.5</v>
@@ -3747,36 +3870,39 @@
         <v>1.09435466583818E-3</v>
       </c>
       <c r="K41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L41" t="s">
+        <v>70</v>
+      </c>
+      <c r="M41" t="s">
         <v>71</v>
       </c>
-      <c r="M41" t="s">
-        <v>72</v>
-      </c>
       <c r="N41" t="s">
+        <v>60</v>
+      </c>
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
         <v>61</v>
       </c>
-      <c r="O41" t="b">
-        <v>1</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>62</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>63</v>
       </c>
-      <c r="R41" t="s">
-        <v>64</v>
-      </c>
       <c r="S41" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="T41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42">
         <v>65</v>
@@ -3785,13 +3911,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E42">
         <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G42">
         <v>7613</v>
@@ -3806,37 +3932,40 @@
         <v>1.3282664585858501E-3</v>
       </c>
       <c r="K42" t="s">
+        <v>77</v>
+      </c>
+      <c r="L42" t="s">
         <v>78</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>79</v>
       </c>
-      <c r="M42" t="s">
-        <v>80</v>
-      </c>
       <c r="N42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
       </c>
       <c r="P42" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q42" t="s">
         <v>59</v>
       </c>
-      <c r="Q42" t="s">
-        <v>60</v>
-      </c>
       <c r="R42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S42" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="T42" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S42" xr:uid="{921EB8AC-600C-6545-A6FA-27BF07546C43}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S42">
-      <sortCondition ref="S1:S42"/>
+  <autoFilter ref="A1:T42" xr:uid="{921EB8AC-600C-6545-A6FA-27BF07546C43}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T42">
+      <sortCondition ref="T1:T42"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A19C9821-8A27-664E-9195-3CA780F7D060}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B145449-27B1-8848-AAB1-C122B20CE127}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="920" windowWidth="28040" windowHeight="17440" xr2:uid="{D28FA05A-120C-6545-B4F5-F747CF17E917}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="158">
   <si>
     <t>k10</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>snDLPFC_PEC</t>
+  </si>
+  <si>
+    <t>cell_type_broad</t>
   </si>
   <si>
     <t>DGE_compat</t>
@@ -1399,30 +1402,30 @@
         <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" t="s">
-        <v>155</v>
-      </c>
       <c r="T1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>10976</v>
@@ -1431,13 +1434,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>9395</v>
@@ -1452,39 +1455,39 @@
         <v>1.0052856523543501E-3</v>
       </c>
       <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" t="s">
         <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>5276</v>
@@ -1493,13 +1496,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>3337</v>
@@ -1514,39 +1517,39 @@
         <v>7.34380388166755E-4</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T3" t="s">
         <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>3087</v>
@@ -1555,13 +1558,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
         <v>5406</v>
@@ -1576,39 +1579,39 @@
         <v>9.2488911468535597E-4</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" t="s">
         <v>33</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" t="s">
-        <v>25</v>
-      </c>
-      <c r="S4" t="s">
-        <v>23</v>
-      </c>
-      <c r="T4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>1133</v>
@@ -1617,13 +1620,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>7658</v>
@@ -1638,34 +1641,34 @@
         <v>1.22074235696345E-3</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S5" t="s">
+        <v>24</v>
+      </c>
+      <c r="T5" t="s">
         <v>37</v>
-      </c>
-      <c r="M5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" t="s">
-        <v>25</v>
-      </c>
-      <c r="S5" t="s">
-        <v>23</v>
-      </c>
-      <c r="T5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -1679,13 +1682,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6">
         <v>1847.5</v>
@@ -1700,39 +1703,39 @@
         <v>7.4577931081876105E-4</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+      <c r="T6" t="s">
         <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" t="s">
-        <v>23</v>
-      </c>
-      <c r="T6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>384</v>
@@ -1741,13 +1744,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7">
         <v>1165</v>
@@ -1762,39 +1765,39 @@
         <v>6.3512404449284001E-4</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>280</v>
@@ -1803,13 +1806,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>14575</v>
@@ -1824,39 +1827,39 @@
         <v>0.99919372797012296</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>81</v>
@@ -1865,13 +1868,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>26876</v>
@@ -1886,39 +1889,39 @@
         <v>0.99924951791763295</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10">
         <v>47</v>
@@ -1927,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>585</v>
@@ -1948,39 +1951,39 @@
         <v>6.7282974487170501E-4</v>
       </c>
       <c r="K10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>47</v>
@@ -1989,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>53380</v>
@@ -2010,39 +2013,39 @@
         <v>0.99924832582473699</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>22</v>
@@ -2051,13 +2054,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>859</v>
@@ -2072,39 +2075,39 @@
         <v>8.3860030281357402E-4</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>433</v>
@@ -2113,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G13">
         <v>4066</v>
@@ -2134,39 +2137,39 @@
         <v>8.0070935655385202E-4</v>
       </c>
       <c r="K13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <v>4227</v>
@@ -2175,13 +2178,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14">
         <v>4598</v>
@@ -2196,39 +2199,39 @@
         <v>7.7069737017154596E-4</v>
       </c>
       <c r="K14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L14" t="s">
+        <v>85</v>
+      </c>
+      <c r="M14" t="s">
+        <v>86</v>
+      </c>
+      <c r="N14" t="s">
+        <v>86</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R14" t="s">
+        <v>88</v>
+      </c>
+      <c r="S14" t="s">
+        <v>86</v>
+      </c>
+      <c r="T14" t="s">
         <v>83</v>
-      </c>
-      <c r="L14" t="s">
-        <v>84</v>
-      </c>
-      <c r="M14" t="s">
-        <v>85</v>
-      </c>
-      <c r="N14" t="s">
-        <v>85</v>
-      </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>85</v>
-      </c>
-      <c r="R14" t="s">
-        <v>87</v>
-      </c>
-      <c r="S14" t="s">
-        <v>85</v>
-      </c>
-      <c r="T14" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>3748</v>
@@ -2237,13 +2240,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G15">
         <v>2557.5</v>
@@ -2258,39 +2261,39 @@
         <v>7.5151113560423201E-4</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L15" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" t="s">
+        <v>91</v>
+      </c>
+      <c r="N15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>86</v>
+      </c>
+      <c r="R15" t="s">
+        <v>92</v>
+      </c>
+      <c r="S15" t="s">
+        <v>86</v>
+      </c>
+      <c r="T15" t="s">
         <v>89</v>
-      </c>
-      <c r="M15" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15" t="s">
-        <v>85</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>85</v>
-      </c>
-      <c r="R15" t="s">
-        <v>91</v>
-      </c>
-      <c r="S15" t="s">
-        <v>85</v>
-      </c>
-      <c r="T15" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>1876</v>
@@ -2299,13 +2302,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16">
         <v>4734.5</v>
@@ -2320,39 +2323,39 @@
         <v>7.9788090079091403E-4</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M16" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" t="s">
+        <v>86</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R16" t="s">
+        <v>81</v>
+      </c>
+      <c r="S16" t="s">
+        <v>86</v>
+      </c>
+      <c r="T16" t="s">
         <v>93</v>
-      </c>
-      <c r="N16" t="s">
-        <v>85</v>
-      </c>
-      <c r="O16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>85</v>
-      </c>
-      <c r="R16" t="s">
-        <v>80</v>
-      </c>
-      <c r="S16" t="s">
-        <v>85</v>
-      </c>
-      <c r="T16" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17">
         <v>1728</v>
@@ -2361,13 +2364,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G17">
         <v>4342.5</v>
@@ -2382,39 +2385,39 @@
         <v>7.7069737017154596E-4</v>
       </c>
       <c r="K17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
       </c>
       <c r="P17" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q17" t="s">
         <v>86</v>
       </c>
-      <c r="Q17" t="s">
-        <v>85</v>
-      </c>
       <c r="R17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>590</v>
@@ -2423,13 +2426,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G18">
         <v>2510</v>
@@ -2444,39 +2447,39 @@
         <v>7.9654873115941795E-4</v>
       </c>
       <c r="K18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L18" t="s">
+        <v>97</v>
+      </c>
+      <c r="M18" t="s">
+        <v>94</v>
+      </c>
+      <c r="N18" t="s">
+        <v>86</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18" t="s">
+        <v>81</v>
+      </c>
+      <c r="S18" t="s">
+        <v>86</v>
+      </c>
+      <c r="T18" t="s">
         <v>96</v>
-      </c>
-      <c r="M18" t="s">
-        <v>93</v>
-      </c>
-      <c r="N18" t="s">
-        <v>85</v>
-      </c>
-      <c r="O18" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>85</v>
-      </c>
-      <c r="R18" t="s">
-        <v>80</v>
-      </c>
-      <c r="S18" t="s">
-        <v>85</v>
-      </c>
-      <c r="T18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>802</v>
@@ -2485,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E19">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G19">
         <v>1497.5</v>
@@ -2506,39 +2509,39 @@
         <v>7.1135553298517997E-4</v>
       </c>
       <c r="K19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>124</v>
@@ -2547,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G20">
         <v>7586.5</v>
@@ -2568,39 +2571,39 @@
         <v>0.99873107671737604</v>
       </c>
       <c r="K20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>12519</v>
@@ -2609,13 +2612,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G21">
         <v>5673</v>
@@ -2630,39 +2633,39 @@
         <v>1.1913639027625301E-3</v>
       </c>
       <c r="K21" t="s">
+        <v>107</v>
+      </c>
+      <c r="L21" t="s">
+        <v>108</v>
+      </c>
+      <c r="M21" t="s">
+        <v>109</v>
+      </c>
+      <c r="N21" t="s">
+        <v>109</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>109</v>
+      </c>
+      <c r="R21" t="s">
+        <v>110</v>
+      </c>
+      <c r="S21" t="s">
+        <v>109</v>
+      </c>
+      <c r="T21" t="s">
         <v>106</v>
-      </c>
-      <c r="L21" t="s">
-        <v>107</v>
-      </c>
-      <c r="M21" t="s">
-        <v>108</v>
-      </c>
-      <c r="N21" t="s">
-        <v>108</v>
-      </c>
-      <c r="O21" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>108</v>
-      </c>
-      <c r="R21" t="s">
-        <v>109</v>
-      </c>
-      <c r="S21" t="s">
-        <v>108</v>
-      </c>
-      <c r="T21" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>12010</v>
@@ -2671,13 +2674,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G22">
         <v>8807</v>
@@ -2692,39 +2695,39 @@
         <v>1.84304174035787E-3</v>
       </c>
       <c r="K22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M22" t="s">
+        <v>109</v>
+      </c>
+      <c r="N22" t="s">
+        <v>109</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>109</v>
+      </c>
+      <c r="R22" t="s">
+        <v>110</v>
+      </c>
+      <c r="S22" t="s">
+        <v>109</v>
+      </c>
+      <c r="T22" t="s">
         <v>111</v>
-      </c>
-      <c r="M22" t="s">
-        <v>108</v>
-      </c>
-      <c r="N22" t="s">
-        <v>108</v>
-      </c>
-      <c r="O22" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>108</v>
-      </c>
-      <c r="R22" t="s">
-        <v>109</v>
-      </c>
-      <c r="S22" t="s">
-        <v>108</v>
-      </c>
-      <c r="T22" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23">
         <v>8587</v>
@@ -2733,13 +2736,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23">
         <v>2161</v>
@@ -2754,39 +2757,39 @@
         <v>7.5151113560423201E-4</v>
       </c>
       <c r="K23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L23" t="s">
+        <v>115</v>
+      </c>
+      <c r="M23" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" t="s">
+        <v>109</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P23" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>109</v>
+      </c>
+      <c r="R23" t="s">
+        <v>116</v>
+      </c>
+      <c r="S23" t="s">
+        <v>109</v>
+      </c>
+      <c r="T23" t="s">
         <v>114</v>
-      </c>
-      <c r="M23" t="s">
-        <v>62</v>
-      </c>
-      <c r="N23" t="s">
-        <v>108</v>
-      </c>
-      <c r="O23" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>108</v>
-      </c>
-      <c r="R23" t="s">
-        <v>115</v>
-      </c>
-      <c r="S23" t="s">
-        <v>108</v>
-      </c>
-      <c r="T23" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24">
         <v>6911</v>
@@ -2795,13 +2798,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G24">
         <v>3616</v>
@@ -2816,39 +2819,39 @@
         <v>9.9148368462920211E-4</v>
       </c>
       <c r="K24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R24" t="s">
+        <v>110</v>
+      </c>
+      <c r="S24" t="s">
         <v>109</v>
       </c>
-      <c r="S24" t="s">
-        <v>108</v>
-      </c>
       <c r="T24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25">
         <v>4254</v>
@@ -2857,13 +2860,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G25">
         <v>3743.5</v>
@@ -2878,39 +2881,39 @@
         <v>9.7419167286716402E-4</v>
       </c>
       <c r="K25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s">
+        <v>119</v>
+      </c>
+      <c r="M25" t="s">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s">
+        <v>109</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>109</v>
+      </c>
+      <c r="R25" t="s">
+        <v>110</v>
+      </c>
+      <c r="S25" t="s">
+        <v>109</v>
+      </c>
+      <c r="T25" t="s">
         <v>118</v>
-      </c>
-      <c r="M25" t="s">
-        <v>119</v>
-      </c>
-      <c r="N25" t="s">
-        <v>108</v>
-      </c>
-      <c r="O25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P25" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>108</v>
-      </c>
-      <c r="R25" t="s">
-        <v>109</v>
-      </c>
-      <c r="S25" t="s">
-        <v>108</v>
-      </c>
-      <c r="T25" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26">
         <v>812</v>
@@ -2919,13 +2922,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E26">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G26">
         <v>1111</v>
@@ -2940,39 +2943,39 @@
         <v>7.02247663866728E-4</v>
       </c>
       <c r="K26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27">
         <v>118</v>
@@ -2981,13 +2984,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27">
         <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G27">
         <v>8577</v>
@@ -3002,39 +3005,39 @@
         <v>0.99896824359893799</v>
       </c>
       <c r="K27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
       <c r="P27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>535</v>
@@ -3043,13 +3046,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28">
         <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G28">
         <v>3158</v>
@@ -3064,39 +3067,39 @@
         <v>1.23374222312122E-3</v>
       </c>
       <c r="K28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
       </c>
       <c r="P28" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q28" t="s">
         <v>123</v>
       </c>
-      <c r="Q28" t="s">
-        <v>122</v>
-      </c>
       <c r="R28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B29">
         <v>427</v>
@@ -3105,13 +3108,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G29">
         <v>6994</v>
@@ -3126,39 +3129,39 @@
         <v>1.19990780949592E-2</v>
       </c>
       <c r="K29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>4815</v>
@@ -3167,13 +3170,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G30">
         <v>8122</v>
@@ -3188,39 +3191,39 @@
         <v>1.0560568189248399E-3</v>
       </c>
       <c r="K30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L30" t="s">
+        <v>140</v>
+      </c>
+      <c r="M30" t="s">
+        <v>141</v>
+      </c>
+      <c r="N30" t="s">
+        <v>129</v>
+      </c>
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>129</v>
+      </c>
+      <c r="R30" t="s">
+        <v>130</v>
+      </c>
+      <c r="S30" t="s">
+        <v>129</v>
+      </c>
+      <c r="T30" t="s">
         <v>139</v>
-      </c>
-      <c r="M30" t="s">
-        <v>140</v>
-      </c>
-      <c r="N30" t="s">
-        <v>128</v>
-      </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>128</v>
-      </c>
-      <c r="R30" t="s">
-        <v>129</v>
-      </c>
-      <c r="S30" t="s">
-        <v>128</v>
-      </c>
-      <c r="T30" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>4009</v>
@@ -3229,13 +3232,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G31">
         <v>4601</v>
@@ -3250,39 +3253,39 @@
         <v>8.0116966273635604E-4</v>
       </c>
       <c r="K31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L31" t="s">
+        <v>143</v>
+      </c>
+      <c r="M31" t="s">
+        <v>144</v>
+      </c>
+      <c r="N31" t="s">
+        <v>129</v>
+      </c>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>129</v>
+      </c>
+      <c r="R31" t="s">
+        <v>130</v>
+      </c>
+      <c r="S31" t="s">
+        <v>129</v>
+      </c>
+      <c r="T31" t="s">
         <v>142</v>
-      </c>
-      <c r="M31" t="s">
-        <v>143</v>
-      </c>
-      <c r="N31" t="s">
-        <v>128</v>
-      </c>
-      <c r="O31" t="b">
-        <v>1</v>
-      </c>
-      <c r="P31" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>128</v>
-      </c>
-      <c r="R31" t="s">
-        <v>129</v>
-      </c>
-      <c r="S31" t="s">
-        <v>128</v>
-      </c>
-      <c r="T31" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32">
         <v>3932</v>
@@ -3291,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G32">
         <v>12043.5</v>
@@ -3312,39 +3315,39 @@
         <v>1.50453706737607E-3</v>
       </c>
       <c r="K32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L32" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" t="s">
+        <v>35</v>
+      </c>
+      <c r="N32" t="s">
+        <v>129</v>
+      </c>
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>129</v>
+      </c>
+      <c r="R32" t="s">
+        <v>130</v>
+      </c>
+      <c r="S32" t="s">
+        <v>129</v>
+      </c>
+      <c r="T32" t="s">
         <v>145</v>
-      </c>
-      <c r="M32" t="s">
-        <v>34</v>
-      </c>
-      <c r="N32" t="s">
-        <v>128</v>
-      </c>
-      <c r="O32" t="b">
-        <v>1</v>
-      </c>
-      <c r="P32" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>128</v>
-      </c>
-      <c r="R32" t="s">
-        <v>129</v>
-      </c>
-      <c r="S32" t="s">
-        <v>128</v>
-      </c>
-      <c r="T32" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B33">
         <v>1961</v>
@@ -3353,13 +3356,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33">
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G33">
         <v>10767</v>
@@ -3374,39 +3377,39 @@
         <v>1.2470565270632501E-3</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s">
+        <v>148</v>
+      </c>
+      <c r="M33" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" t="s">
+        <v>129</v>
+      </c>
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>129</v>
+      </c>
+      <c r="R33" t="s">
+        <v>130</v>
+      </c>
+      <c r="S33" t="s">
+        <v>129</v>
+      </c>
+      <c r="T33" t="s">
         <v>147</v>
-      </c>
-      <c r="M33" t="s">
-        <v>34</v>
-      </c>
-      <c r="N33" t="s">
-        <v>128</v>
-      </c>
-      <c r="O33" t="b">
-        <v>1</v>
-      </c>
-      <c r="P33" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>128</v>
-      </c>
-      <c r="R33" t="s">
-        <v>129</v>
-      </c>
-      <c r="S33" t="s">
-        <v>128</v>
-      </c>
-      <c r="T33" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B34">
         <v>458</v>
@@ -3415,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34">
         <v>2204</v>
@@ -3436,39 +3439,39 @@
         <v>6.5941060893237504E-4</v>
       </c>
       <c r="K34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M34" t="s">
+        <v>129</v>
+      </c>
+      <c r="N34" t="s">
+        <v>109</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
         <v>128</v>
       </c>
-      <c r="N34" t="s">
-        <v>108</v>
-      </c>
-      <c r="O34" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34" t="s">
-        <v>127</v>
-      </c>
       <c r="Q34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R34" t="s">
+        <v>130</v>
+      </c>
+      <c r="S34" t="s">
         <v>129</v>
       </c>
-      <c r="S34" t="s">
-        <v>128</v>
-      </c>
       <c r="T34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B35">
         <v>345</v>
@@ -3477,13 +3480,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G35">
         <v>7872</v>
@@ -3498,39 +3501,39 @@
         <v>1.4534917427226901E-3</v>
       </c>
       <c r="K35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B36">
         <v>41</v>
@@ -3539,13 +3542,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G36">
         <v>7117</v>
@@ -3560,34 +3563,34 @@
         <v>1.4361247885972201E-3</v>
       </c>
       <c r="K36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
       <c r="P36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
@@ -3601,13 +3604,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E37">
         <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37">
         <v>4861.5</v>
@@ -3622,39 +3625,39 @@
         <v>1.1913639027625301E-3</v>
       </c>
       <c r="K37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38">
         <v>147</v>
@@ -3663,13 +3666,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G38">
         <v>6357</v>
@@ -3684,39 +3687,39 @@
         <v>1.4223176985979E-3</v>
       </c>
       <c r="K38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
       </c>
       <c r="P38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39">
         <v>352</v>
@@ -3725,13 +3728,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G39">
         <v>5216.5</v>
@@ -3746,39 +3749,39 @@
         <v>1.0071775759570301E-3</v>
       </c>
       <c r="K39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>286</v>
@@ -3787,13 +3790,13 @@
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G40">
         <v>8664</v>
@@ -3808,39 +3811,39 @@
         <v>1.2288140133023199E-3</v>
       </c>
       <c r="K40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M40" t="s">
+        <v>63</v>
+      </c>
+      <c r="N40" t="s">
+        <v>61</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" t="s">
         <v>62</v>
       </c>
-      <c r="N40" t="s">
-        <v>60</v>
-      </c>
-      <c r="O40" t="b">
-        <v>1</v>
-      </c>
-      <c r="P40" t="s">
-        <v>61</v>
-      </c>
       <c r="Q40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B41">
         <v>212</v>
@@ -3849,13 +3852,13 @@
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E41">
         <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G41">
         <v>6566.5</v>
@@ -3870,39 +3873,39 @@
         <v>1.09435466583818E-3</v>
       </c>
       <c r="K41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O41" t="b">
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B42">
         <v>65</v>
@@ -3911,13 +3914,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42">
         <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G42">
         <v>7613</v>
@@ -3932,34 +3935,34 @@
         <v>1.3282664585858501E-3</v>
       </c>
       <c r="K42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
+++ b/processed-data/04_snRNA-seq/27_sn_gila_check/ERCsn_glia_subcluster_info_anno.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/04_snRNA-seq/27_sn_gila_check/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B145449-27B1-8848-AAB1-C122B20CE127}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{81983764-2818-1A4A-939C-A37722A8AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72FE032F-0532-2E43-888A-17E32BFD7A98}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="920" windowWidth="28040" windowHeight="17440" xr2:uid="{D28FA05A-120C-6545-B4F5-F747CF17E917}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="168">
   <si>
     <t>k10</t>
   </si>
@@ -497,6 +497,36 @@
   </si>
   <si>
     <t>Vasc</t>
+  </si>
+  <si>
+    <t>Astro.1</t>
+  </si>
+  <si>
+    <t>Astro.2</t>
+  </si>
+  <si>
+    <t>Astro.3</t>
+  </si>
+  <si>
+    <t>Astro.4</t>
+  </si>
+  <si>
+    <t>Astro.5</t>
+  </si>
+  <si>
+    <t>Oligo.1</t>
+  </si>
+  <si>
+    <t>Oligo.2</t>
+  </si>
+  <si>
+    <t>Oligo.3</t>
+  </si>
+  <si>
+    <t>Oligo.4</t>
+  </si>
+  <si>
+    <t>Oligo.5</t>
   </si>
 </sst>
 </file>
@@ -1041,6 +1071,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1360,6 +1394,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921EB8AC-600C-6545-A6FA-27BF07546C43}">
   <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="20" max="20" width="15.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1482,7 +1519,7 @@
         <v>24</v>
       </c>
       <c r="T2" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
@@ -1544,7 +1581,7 @@
         <v>24</v>
       </c>
       <c r="T3" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
@@ -1606,7 +1643,7 @@
         <v>24</v>
       </c>
       <c r="T4" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
@@ -1668,7 +1705,7 @@
         <v>24</v>
       </c>
       <c r="T5" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
@@ -1730,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="T6" t="s">
-        <v>41</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
@@ -2660,7 +2697,7 @@
         <v>109</v>
       </c>
       <c r="T21" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -2722,7 +2759,7 @@
         <v>109</v>
       </c>
       <c r="T22" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
@@ -2784,7 +2821,7 @@
         <v>109</v>
       </c>
       <c r="T23" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
@@ -2846,7 +2883,7 @@
         <v>109</v>
       </c>
       <c r="T24" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -2908,7 +2945,7 @@
         <v>109</v>
       </c>
       <c r="T25" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
